--- a/data/trans_dic/P64D$publico_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,46</t>
+          <t>1,83; 8,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,16</t>
+          <t>1,0; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,29</t>
+          <t>1,87; 6,17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,78</t>
+          <t>2,23; 10,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,36</t>
+          <t>2,97; 12,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,98</t>
+          <t>3,24; 8,62</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 17,83</t>
+          <t>6,25; 16,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,96</t>
+          <t>3,38; 8,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,28</t>
+          <t>0,44; 5,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,75</t>
+          <t>1,43; 8,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,71</t>
+          <t>1,57; 5,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,11</t>
+          <t>1,27; 7,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,28; 2,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,38</t>
+          <t>0,97; 4,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,36</t>
+          <t>0,07; 2,15</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,14</t>
+          <t>3,29; 9,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,65</t>
+          <t>6,83; 12,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,77</t>
+          <t>5,62; 9,57</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 22,56</t>
+          <t>4,4; 22,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,51; 35,51</t>
+          <t>24,53; 35,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 25,38</t>
+          <t>8,65; 25,51</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,06</t>
+          <t>4,11; 8,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,15</t>
+          <t>8,21; 11,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,33</t>
+          <t>6,33; 9,28</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3521; 16251</t>
+          <t>3523; 16732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1483; 10333</t>
+          <t>1442; 9834</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6424; 21154</t>
+          <t>6295; 20771</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5719; 24027</t>
+          <t>5487; 24744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4435; 18815</t>
+          <t>4918; 20516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13719; 36929</t>
+          <t>13316; 35435</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6413</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7598; 21545</t>
+          <t>7552; 19751</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8603; 24145</t>
+          <t>9121; 23463</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>740; 8842</t>
+          <t>735; 8377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3973; 22642</t>
+          <t>3696; 21784</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6664; 24342</t>
+          <t>6670; 23935</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1409; 9264</t>
+          <t>1447; 9032</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>311; 2862</t>
+          <t>303; 2644</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1959; 9690</t>
+          <t>2140; 9989</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 836</t>
+          <t>0; 786</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 4580</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165; 5224</t>
+          <t>163; 4771</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10969; 30561</t>
+          <t>11002; 31859</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20288; 38803</t>
+          <t>20939; 39286</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35507; 62644</t>
+          <t>36031; 61367</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30327; 141721</t>
+          <t>27631; 140442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66441; 96252</t>
+          <t>66499; 96085</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67624; 228238</t>
+          <t>77805; 229459</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>83786; 158391</t>
+          <t>80741; 158237</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>122483; 177543</t>
+          <t>119889; 174491</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>213515; 319655</t>
+          <t>217072; 317880</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$publico_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,71</t>
+          <t>1,47; 6,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,81</t>
+          <t>1,02; 5,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,17</t>
+          <t>1,83; 5,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,08</t>
+          <t>2,25; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,39</t>
+          <t>2,9; 11,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,62</t>
+          <t>3,2; 8,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 16,34</t>
+          <t>5,79; 16,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,7</t>
+          <t>3,21; 8,34</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,0</t>
+          <t>0,35; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,42</t>
+          <t>4,13; 12,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,62</t>
+          <t>2,45; 6,36</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,91</t>
+          <t>2,14; 9,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,47</t>
+          <t>0,4; 4,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,51</t>
+          <t>1,73; 5,89</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,15</t>
+          <t>0,28; 2,5</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,53</t>
+          <t>4,4; 10,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,81</t>
+          <t>7,15; 13,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,57</t>
+          <t>6,25; 10,59</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 22,35</t>
+          <t>18,15; 26,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,53; 35,44</t>
+          <t>24,95; 35,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,65; 25,51</t>
+          <t>21,98; 28,11</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,05</t>
+          <t>6,88; 9,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,94</t>
+          <t>9,91; 12,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,28</t>
+          <t>8,57; 10,66</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>11141</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3523; 16732</t>
+          <t>2941; 13505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1442; 9834</t>
+          <t>1552; 8629</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6295; 20771</t>
+          <t>6465; 18101</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22758</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5487; 24744</t>
+          <t>5740; 25456</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4918; 20516</t>
+          <t>5037; 19802</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13316; 35435</t>
+          <t>13714; 36262</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14525</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6985</t>
+          <t>0; 6909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7552; 19751</t>
+          <t>7120; 20534</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9121; 23463</t>
+          <t>8757; 22736</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>15920</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>735; 8377</t>
+          <t>739; 7347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3696; 21784</t>
+          <t>7482; 21890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6670; 23935</t>
+          <t>9578; 24885</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>8506</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1447; 9032</t>
+          <t>2908; 13166</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>303; 2644</t>
+          <t>478; 5414</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2140; 9989</t>
+          <t>4410; 15056</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>880</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>2132</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 786</t>
+          <t>0; 4481</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163; 4771</t>
+          <t>615; 5589</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>63495</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11002; 31859</t>
+          <t>17042; 42469</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20939; 39286</t>
+          <t>25884; 48921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36031; 61367</t>
+          <t>46837; 79364</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>80237</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160464</t>
+          <t>192858</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27631; 140442</t>
+          <t>82577; 119604</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66499; 96085</t>
+          <t>77890; 109567</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77805; 229459</t>
+          <t>168578; 215596</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>80741; 158237</t>
+          <t>132684; 189371</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119889; 174491</t>
+          <t>149700; 195560</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>217072; 317880</t>
+          <t>294712; 366744</t>
         </is>
       </c>
     </row>
